--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N226_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N226_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>88.17784449165789</v>
+        <v>14.32889972989441</v>
       </c>
       <c r="D2" t="n">
-        <v>43.83206588788623</v>
+        <v>7.122710706781513</v>
       </c>
       <c r="E2" t="n">
-        <v>22.81054794424909</v>
+        <v>3.706714040940477</v>
       </c>
       <c r="F2" t="n">
-        <v>15.06554142676107</v>
+        <v>2.448150481848674</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>51.28269084272996</v>
+        <v>8.333437261943619</v>
       </c>
       <c r="D3" t="n">
-        <v>55.32779418918753</v>
+        <v>8.990766555742974</v>
       </c>
       <c r="E3" t="n">
-        <v>22.81054794424909</v>
+        <v>3.706714040940477</v>
       </c>
       <c r="F3" t="n">
-        <v>15.06554142676107</v>
+        <v>2.448150481848674</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>52.58093382699906</v>
+        <v>8.544401746887349</v>
       </c>
       <c r="D4" t="n">
-        <v>9.486832980505138</v>
+        <v>1.541610359332085</v>
       </c>
       <c r="E4" t="n">
-        <v>22.81054794424909</v>
+        <v>3.706714040940477</v>
       </c>
       <c r="F4" t="n">
-        <v>15.06554142676107</v>
+        <v>2.448150481848674</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>43.78117408370353</v>
+        <v>7.114440788601823</v>
       </c>
       <c r="D5" t="n">
-        <v>4.202871415125264</v>
+        <v>0.6829666049578554</v>
       </c>
       <c r="E5" t="n">
-        <v>22.81054794424909</v>
+        <v>3.706714040940477</v>
       </c>
       <c r="F5" t="n">
-        <v>15.06554142676107</v>
+        <v>2.448150481848674</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>34.52507618820912</v>
+        <v>5.610324880583982</v>
       </c>
       <c r="D6" t="n">
-        <v>16.19413474070165</v>
+        <v>2.631546895364018</v>
       </c>
       <c r="E6" t="n">
-        <v>22.81054794424909</v>
+        <v>3.706714040940477</v>
       </c>
       <c r="F6" t="n">
-        <v>15.06554142676107</v>
+        <v>2.448150481848674</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>37.1528467345255</v>
+        <v>6.037337594360395</v>
       </c>
       <c r="D7" t="n">
-        <v>40.33902824485846</v>
+        <v>6.5550920897895</v>
       </c>
       <c r="E7" t="n">
-        <v>22.81054794424909</v>
+        <v>3.706714040940477</v>
       </c>
       <c r="F7" t="n">
-        <v>15.06554142676107</v>
+        <v>2.448150481848674</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>47.98301310592365</v>
+        <v>7.797239629712593</v>
       </c>
       <c r="D8" t="n">
-        <v>31.43139177145538</v>
+        <v>5.107601162861499</v>
       </c>
       <c r="E8" t="n">
-        <v>22.81054794424909</v>
+        <v>3.706714040940477</v>
       </c>
       <c r="F8" t="n">
-        <v>15.06554142676107</v>
+        <v>2.448150481848674</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>24.34101189904313</v>
+        <v>3.955414433594509</v>
       </c>
       <c r="D9" t="n">
-        <v>20.54149953692809</v>
+        <v>3.337993674750815</v>
       </c>
       <c r="E9" t="n">
-        <v>22.81054794424909</v>
+        <v>3.706714040940477</v>
       </c>
       <c r="F9" t="n">
-        <v>15.06554142676107</v>
+        <v>2.448150481848674</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>36.68463244268852</v>
+        <v>5.961252771936884</v>
       </c>
       <c r="D10" t="n">
-        <v>37.14610213675329</v>
+        <v>6.036241597222409</v>
       </c>
       <c r="E10" t="n">
-        <v>22.81054794424909</v>
+        <v>3.706714040940477</v>
       </c>
       <c r="F10" t="n">
-        <v>15.06554142676107</v>
+        <v>2.448150481848674</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>49.0446915849477</v>
+        <v>7.969762382554001</v>
       </c>
       <c r="D11" t="n">
-        <v>45.58220032416011</v>
+        <v>7.407107552676019</v>
       </c>
       <c r="E11" t="n">
-        <v>22.81054794424909</v>
+        <v>3.706714040940477</v>
       </c>
       <c r="F11" t="n">
-        <v>15.06554142676107</v>
+        <v>2.448150481848674</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>46.08467551002373</v>
+        <v>7.488759770378856</v>
       </c>
       <c r="D12" t="n">
-        <v>42.56977860164183</v>
+        <v>6.917589022766798</v>
       </c>
       <c r="E12" t="n">
-        <v>22.81054794424909</v>
+        <v>3.706714040940477</v>
       </c>
       <c r="F12" t="n">
-        <v>15.06554142676107</v>
+        <v>2.448150481848674</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>24.37483729319777</v>
+        <v>3.960911060144638</v>
       </c>
       <c r="D13" t="n">
-        <v>22.41778099504194</v>
+        <v>3.642889411694315</v>
       </c>
       <c r="E13" t="n">
-        <v>22.81054794424909</v>
+        <v>3.706714040940477</v>
       </c>
       <c r="F13" t="n">
-        <v>15.06554142676107</v>
+        <v>2.448150481848674</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>60.82560325480225</v>
+        <v>9.884160528905367</v>
       </c>
       <c r="D14" t="n">
-        <v>38.30871497961709</v>
+        <v>6.225166184187778</v>
       </c>
       <c r="E14" t="n">
-        <v>22.81054794424909</v>
+        <v>3.706714040940477</v>
       </c>
       <c r="F14" t="n">
-        <v>15.06554142676107</v>
+        <v>2.448150481848674</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>61.41895615987982</v>
+        <v>9.980580375980471</v>
       </c>
       <c r="D15" t="n">
-        <v>8.902246907382429</v>
+        <v>1.446615122449645</v>
       </c>
       <c r="E15" t="n">
-        <v>22.81054794424909</v>
+        <v>3.706714040940477</v>
       </c>
       <c r="F15" t="n">
-        <v>15.06554142676107</v>
+        <v>2.448150481848674</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>79.20934925181474</v>
+        <v>12.8715192534199</v>
       </c>
       <c r="D16" t="n">
-        <v>10.54751155486449</v>
+        <v>1.71397062766548</v>
       </c>
       <c r="E16" t="n">
-        <v>22.81054794424909</v>
+        <v>3.706714040940477</v>
       </c>
       <c r="F16" t="n">
-        <v>15.06554142676107</v>
+        <v>2.448150481848674</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>76.52006530049259</v>
+        <v>12.43451061133005</v>
       </c>
       <c r="D17" t="n">
-        <v>16.47479795883252</v>
+        <v>2.677154668310285</v>
       </c>
       <c r="E17" t="n">
-        <v>22.81054794424909</v>
+        <v>3.706714040940477</v>
       </c>
       <c r="F17" t="n">
-        <v>15.06554142676107</v>
+        <v>2.448150481848674</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>87.44090083937908</v>
+        <v>14.2091463863991</v>
       </c>
       <c r="D18" t="n">
-        <v>13.57860644339608</v>
+        <v>2.206523547051864</v>
       </c>
       <c r="E18" t="n">
-        <v>22.81054794424909</v>
+        <v>3.706714040940477</v>
       </c>
       <c r="F18" t="n">
-        <v>15.06554142676107</v>
+        <v>2.448150481848674</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>88.70037645900288</v>
+        <v>14.41381117458797</v>
       </c>
       <c r="D19" t="n">
-        <v>18.08571223957436</v>
+        <v>2.938928238930833</v>
       </c>
       <c r="E19" t="n">
-        <v>22.81054794424909</v>
+        <v>3.706714040940477</v>
       </c>
       <c r="F19" t="n">
-        <v>15.06554142676107</v>
+        <v>2.448150481848674</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>91.98137951115686</v>
+        <v>14.94697417056299</v>
       </c>
       <c r="D20" t="n">
-        <v>5.492199070060646</v>
+        <v>0.8924823488848551</v>
       </c>
       <c r="E20" t="n">
-        <v>22.81054794424909</v>
+        <v>3.706714040940477</v>
       </c>
       <c r="F20" t="n">
-        <v>15.06554142676107</v>
+        <v>2.448150481848674</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>95.84909294285603</v>
+        <v>15.57547760321411</v>
       </c>
       <c r="D21" t="n">
-        <v>17.59827315386823</v>
+        <v>2.859719387503588</v>
       </c>
       <c r="E21" t="n">
-        <v>22.81054794424909</v>
+        <v>3.706714040940477</v>
       </c>
       <c r="F21" t="n">
-        <v>15.06554142676107</v>
+        <v>2.448150481848674</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
